--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:35</t>
+    <t xml:space="preserve">2026-09-09 22:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:21</t>
+    <t xml:space="preserve">2026-09-12 19:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:38</t>
+    <t xml:space="preserve">2026-09-24 00:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:15</t>
+    <t xml:space="preserve">2026-09-27 22:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:04</t>
+    <t xml:space="preserve">2026-09-29 10:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -568,7 +568,7 @@
         <v>2019</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>18.47</v>
+        <v>184.74</v>
       </c>
     </row>
     <row r="3">
@@ -585,7 +585,7 @@
         <v>2019</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>14.67</v>
+        <v>146.69</v>
       </c>
     </row>
     <row r="4">
@@ -602,7 +602,7 @@
         <v>2019</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>14.27</v>
+        <v>142.66</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
         <v>2019</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13.35</v>
+        <v>133.54</v>
       </c>
     </row>
     <row r="6">
@@ -636,7 +636,7 @@
         <v>2019</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>13.09</v>
+        <v>130.87</v>
       </c>
     </row>
     <row r="7">
@@ -653,7 +653,7 @@
         <v>2019</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>12.58</v>
+        <v>125.82</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         <v>2019</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>12.48</v>
+        <v>124.76</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         <v>2019</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>12.47</v>
+        <v>124.69</v>
       </c>
     </row>
     <row r="10">
@@ -704,7 +704,7 @@
         <v>2019</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>11.87</v>
+        <v>118.74</v>
       </c>
     </row>
     <row r="11">
@@ -721,7 +721,7 @@
         <v>2019</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>11.21</v>
+        <v>112.1</v>
       </c>
     </row>
     <row r="12">
@@ -738,7 +738,7 @@
         <v>2019</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>11.2</v>
+        <v>111.99</v>
       </c>
     </row>
     <row r="13">
@@ -755,7 +755,7 @@
         <v>2019</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>10.55</v>
+        <v>105.49</v>
       </c>
     </row>
     <row r="14">
@@ -772,7 +772,7 @@
         <v>2019</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>10.45</v>
+        <v>104.51</v>
       </c>
     </row>
     <row r="15">
@@ -789,7 +789,7 @@
         <v>2019</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>10.22</v>
+        <v>102.21</v>
       </c>
     </row>
     <row r="16">
@@ -806,7 +806,7 @@
         <v>2019</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>9.83</v>
+        <v>98.28</v>
       </c>
     </row>
     <row r="17">
@@ -823,7 +823,7 @@
         <v>2019</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>9.75</v>
+        <v>97.53</v>
       </c>
     </row>
     <row r="18">
@@ -840,7 +840,7 @@
         <v>2019</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>9.67</v>
+        <v>96.71</v>
       </c>
     </row>
     <row r="19">
@@ -857,7 +857,7 @@
         <v>2019</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>9.41</v>
+        <v>94.12</v>
       </c>
     </row>
     <row r="20">
@@ -874,7 +874,7 @@
         <v>2019</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>9.27</v>
+        <v>92.69</v>
       </c>
     </row>
     <row r="21">
@@ -891,7 +891,7 @@
         <v>2019</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>9.23</v>
+        <v>92.34</v>
       </c>
     </row>
     <row r="22">
@@ -908,7 +908,7 @@
         <v>2019</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>9.23</v>
+        <v>92.28</v>
       </c>
     </row>
     <row r="23">
@@ -925,7 +925,7 @@
         <v>2019</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>9.05</v>
+        <v>90.53</v>
       </c>
     </row>
     <row r="24">
@@ -942,7 +942,7 @@
         <v>2019</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>8.97</v>
+        <v>89.69</v>
       </c>
     </row>
     <row r="25">
@@ -959,7 +959,7 @@
         <v>2019</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>8.93</v>
+        <v>89.28</v>
       </c>
     </row>
     <row r="26">
@@ -976,7 +976,7 @@
         <v>2019</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>8.79</v>
+        <v>87.92</v>
       </c>
     </row>
     <row r="27">
@@ -993,7 +993,7 @@
         <v>2019</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>8.24</v>
+        <v>82.4</v>
       </c>
     </row>
     <row r="28">
@@ -1010,7 +1010,7 @@
         <v>2019</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>7.85</v>
+        <v>78.52</v>
       </c>
     </row>
     <row r="29">
@@ -1027,7 +1027,7 @@
         <v>2019</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>7.62</v>
+        <v>76.19</v>
       </c>
     </row>
     <row r="30">
@@ -1044,7 +1044,7 @@
         <v>2019</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>7.56</v>
+        <v>75.58</v>
       </c>
     </row>
     <row r="31">
@@ -1061,7 +1061,7 @@
         <v>2019</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>6.95</v>
+        <v>69.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 10:59</t>
+    <t xml:space="preserve">2026-10-01 19:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:23</t>
+    <t xml:space="preserve">2026-10-02 13:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:05</t>
+    <t xml:space="preserve">2026-10-05 07:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
